--- a/measures.xlsx
+++ b/measures.xlsx
@@ -476,22 +476,9 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>VAR CurrentWeek =
-    MAX ( passing[week] )
-VAR ThisWeek =
-    CALCULATE (
-        SUM ( passing[yards] ),
-        passing[week] = CurrentWeek
-    )
-VAR LastWeek =
-    CALCULATE (
-        SUM ( passing[yards] ),
-        passing[week] = CurrentWeek - 1
-    )
-RETURN
-    ThisWeek - COALESCE ( LastWeek, 0 )</t>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CALCULATE(SUM(passing[yards]), passing[week] = MAX(passing[week]))</t>
         </is>
       </c>
       <c r="G7"/>
@@ -545,15 +532,9 @@
           <t>Number</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>DIVIDE (
-    CALCULATE (
-        SUM ( passing[yards] ),
-        passing[week] = MAX ( passing[week] )
-    ),
-    MAX ( passing[week] )
-)</t>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>AVERAGEX(VALUES(passing[week]), CALCULATE(SUM(passing[yards])))</t>
         </is>
       </c>
       <c r="G8"/>
@@ -833,22 +814,9 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>VAR CurrentWeek =
-    MAX ( passing[week] )
-VAR ThisWeek =
-    CALCULATE (
-        SUM ( passing[completions] ),
-        passing[week] = CurrentWeek
-    )
-VAR LastWeek =
-    CALCULATE (
-        SUM ( passing[completions] ),
-        passing[week] = CurrentWeek - 1
-    )
-RETURN
-    ThisWeek - COALESCE ( LastWeek, 0 )</t>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CALCULATE(SUM(passing[attempts]), passing[week] = MAX(passing[week]))</t>
         </is>
       </c>
       <c r="G13"/>
@@ -1438,15 +1406,8 @@
       <c r="F23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">
-VAR CurrentWeek = MAX(kicking[week])
-RETURN
-    COALESCE(
-        CALCULATE(
-            MAX(kicking[field_goal_long]),
-            kicking[week] = CurrentWeek
-        ),
-        0
-    )</t>
+VAR CurrentWeek = MAX(kicking[week]) 
+RETURN CALCULATE(MAX(kicking[field_goal_long]), kicking[week] &lt;= CurrentWeek, ALL(kicking[week]))</t>
         </is>
       </c>
       <c r="G23"/>
